--- a/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_06-16-26.xlsx
+++ b/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_06-16-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\T41\T41_V012_Files\T41_V012_BOMs\Source Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB543031-C3E3-439A-BD0D-5E1ECB7EFBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CF5D22-1ACB-4369-A9B8-6A7FEA863529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="As Second RX" sheetId="9" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Complete RF Board'!$A$1:$H$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Complete RF Board'!$A$1:$H$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="296">
   <si>
     <t>Qty</t>
   </si>
@@ -78,9 +78,6 @@
     <t>10uF 50V SMD 1206 Capacitor</t>
   </si>
   <si>
-    <t>C1, C3, C11, C12, C14, C32, C35, C36, C39, C41, C42, C48, C51, C57, C60, C67, C71</t>
-  </si>
-  <si>
     <t>80-C1206C106K4P</t>
   </si>
   <si>
@@ -117,12 +114,6 @@
     <t>80-C1206C103K5R7210</t>
   </si>
   <si>
-    <t>C1206C103K5RAC7210</t>
-  </si>
-  <si>
-    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 50V 0.01uF X7R 1206 10%</t>
-  </si>
-  <si>
     <t>80-C1206C680J5HACTU</t>
   </si>
   <si>
@@ -487,9 +478,6 @@
   </si>
   <si>
     <t>0 Ohm SMD 1206 Resistor</t>
-  </si>
-  <si>
-    <t>R40, R42</t>
   </si>
   <si>
     <t>71-CRCW12060000Z0EAC</t>
@@ -912,18 +900,9 @@
     <t>TP1, TP2, TP3, TP4, TP5, TP6, TP7, TP8, TP9, TP10, TP11, TP12, TP13, TP14, TP17, TP18</t>
   </si>
   <si>
-    <t>C6, C7, C13, C16, C18, C20, C22, C23, C25, C26, C27, C29, C30, C31, C40, C43, C45, C47, C53, C55, C56, C58, C59, C61, C62, C63, C64, C65, C68, C70, C72, C73, C80, C85</t>
-  </si>
-  <si>
-    <t>L1, L2, L3, L5, L6, L8, L9</t>
-  </si>
-  <si>
     <t>Oscillator Module, premade</t>
   </si>
   <si>
-    <t>R24, R28, R35, R37, R40, R42, R53, R55</t>
-  </si>
-  <si>
     <t>Attenuator Modules, premade</t>
   </si>
   <si>
@@ -943,6 +922,24 @@
   </si>
   <si>
     <t>Attenuator Module, premade</t>
+  </si>
+  <si>
+    <t>L1, L2, L3, L5, L6, L7, L8, L9</t>
+  </si>
+  <si>
+    <t>C6, C7, C13, C16, C18, C20, C22, C23, C25, C26, C27, C29, C30, C31, C40, C43, C45, C47, C53, C55, C56, C58, C59, C61, C62, C63, C64, C65, C68, C70, C72, C73, C80</t>
+  </si>
+  <si>
+    <t>C1, C3, C11, C12, C14, C32, C35, C36, C39, C41, C42, C57, C60, C67, C71</t>
+  </si>
+  <si>
+    <t>R24, R28, R35, R37, R40, R42, R53, R55, R64, R65, R66, R67</t>
+  </si>
+  <si>
+    <t>603-RC1206FR-130RL</t>
+  </si>
+  <si>
+    <t>R40, R42, R64, R65</t>
   </si>
 </sst>
 </file>
@@ -1410,7 +1407,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1" customWidth="1"/>
@@ -1466,35 +1463,35 @@
     </row>
     <row r="2" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
       </c>
       <c r="G2" s="5">
         <v>0.13900000000000001</v>
       </c>
       <c r="H2" s="5">
-        <f t="shared" ref="H2:H32" si="0">G2*A2</f>
-        <v>2.3630000000000004</v>
+        <f t="shared" ref="H2:H31" si="0">G2*A2</f>
+        <v>2.085</v>
       </c>
       <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>14</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -1502,13 +1499,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G3" s="5">
         <v>0.1</v>
@@ -1523,13 +1520,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" t="s">
         <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
       </c>
       <c r="G4" s="5">
         <v>0.15</v>
@@ -1539,16 +1536,16 @@
         <v>0.6</v>
       </c>
       <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>20</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>21</v>
-      </c>
-      <c r="L4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -1556,62 +1553,62 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>267</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="H5" s="5">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="D6" t="s">
-        <v>275</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+        <v>263</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" t="s">
         <v>262</v>
-      </c>
-      <c r="D7" t="s">
-        <v>267</v>
       </c>
       <c r="G7" s="5">
         <v>0.17</v>
@@ -1620,137 +1617,137 @@
         <f t="shared" si="0"/>
         <v>0.34</v>
       </c>
-      <c r="I7" t="s">
+    </row>
+    <row r="8" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="J7" t="s">
+      <c r="C8" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="K7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="G8" s="5">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="0"/>
+        <v>1.782</v>
+      </c>
+      <c r="I8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>265</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D8" t="s">
-        <v>266</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0.17</v>
-      </c>
-      <c r="H8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="J8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="0"/>
+        <v>1.52</v>
+      </c>
+      <c r="I9" t="s">
         <v>34</v>
       </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="5">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="H9" s="5">
-        <f t="shared" si="0"/>
-        <v>1.8360000000000001</v>
-      </c>
-      <c r="I9" t="s">
-        <v>32</v>
-      </c>
       <c r="J9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K9" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G10" s="5">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" si="0"/>
-        <v>1.52</v>
+        <v>0.39</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G11" s="5">
-        <v>0.39</v>
+        <v>1.41</v>
       </c>
       <c r="H11" s="5">
         <f t="shared" si="0"/>
-        <v>0.39</v>
+        <v>2.82</v>
       </c>
       <c r="I11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -1758,68 +1755,56 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
       </c>
       <c r="G12" s="5">
-        <v>1.41</v>
+        <v>3.35</v>
       </c>
       <c r="H12" s="5">
         <f t="shared" si="0"/>
-        <v>2.82</v>
+        <v>6.7</v>
       </c>
       <c r="I12" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J12" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>57</v>
+        <v>60</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
       </c>
       <c r="G13" s="5">
-        <v>3.35</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H13" s="5">
         <f t="shared" si="0"/>
-        <v>6.7</v>
-      </c>
-      <c r="I13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" t="s">
-        <v>59</v>
-      </c>
-      <c r="K13" t="s">
-        <v>60</v>
-      </c>
-      <c r="L13" t="s">
-        <v>61</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1832,15 +1817,27 @@
       <c r="C14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F14" t="s">
+      <c r="D14" t="s">
         <v>64</v>
       </c>
       <c r="G14" s="5">
-        <v>0.14000000000000001</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="I14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -1848,529 +1845,529 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" t="s">
-        <v>67</v>
+        <v>249</v>
+      </c>
+      <c r="F15" t="s">
+        <v>70</v>
       </c>
       <c r="G15" s="5">
-        <v>1.1200000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="H15" s="5">
         <f t="shared" si="0"/>
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="I15" t="s">
-        <v>67</v>
-      </c>
-      <c r="J15" t="s">
-        <v>68</v>
-      </c>
-      <c r="K15" t="s">
-        <v>69</v>
-      </c>
-      <c r="L15" t="s">
-        <v>70</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>254</v>
+        <v>73</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F16" t="s">
-        <v>73</v>
+        <v>290</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
       </c>
       <c r="G16" s="5">
-        <v>0.02</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H16" s="5">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="I16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L16" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G17" s="5">
-        <v>0.14000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="H17" s="5">
         <f t="shared" si="0"/>
-        <v>0.98000000000000009</v>
+        <v>0.7</v>
       </c>
       <c r="I17" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" t="s">
+        <v>266</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="H18" s="5">
+        <f t="shared" si="0"/>
+        <v>1.41</v>
+      </c>
+      <c r="I18" t="s">
+        <v>85</v>
+      </c>
+      <c r="J18" t="s">
+        <v>86</v>
+      </c>
+      <c r="K18" t="s">
         <v>82</v>
       </c>
-      <c r="D18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="5">
-        <v>0.35</v>
-      </c>
-      <c r="H18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="I18" t="s">
-        <v>83</v>
-      </c>
-      <c r="J18" t="s">
-        <v>84</v>
-      </c>
-      <c r="K18" t="s">
-        <v>85</v>
-      </c>
       <c r="L18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>268</v>
+        <v>88</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>269</v>
-      </c>
-      <c r="E19" t="s">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="G19" s="5">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="H19" s="5">
         <f t="shared" si="0"/>
-        <v>1.41</v>
+        <v>0.37</v>
       </c>
       <c r="I19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="L19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G20" s="5">
-        <v>0.37</v>
+        <v>0.59</v>
       </c>
       <c r="H20" s="5">
         <f t="shared" si="0"/>
-        <v>0.37</v>
+        <v>1.18</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J20" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K20" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="L20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G21" s="5">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="H21" s="5">
         <f t="shared" si="0"/>
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="I21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K21" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="L21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G22" s="5">
         <v>0.1</v>
       </c>
       <c r="H22" s="5">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J22" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>109</v>
+        <v>235</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G23" s="5">
-        <v>0.1</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H23" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="I23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>239</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G24" s="5">
-        <v>1.7000000000000001E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H24" s="5">
         <f t="shared" si="0"/>
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K24" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="L24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G25" s="5">
         <v>0.1</v>
       </c>
       <c r="H25" s="5">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J25" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K25" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="L25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G26" s="5">
         <v>0.1</v>
       </c>
       <c r="H26" s="5">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="I26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J26" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K26" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G27" s="5">
-        <v>0.1</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="H27" s="5">
         <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+        <v>0.36</v>
       </c>
       <c r="I27" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J27" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K27" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="L27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D28" t="s">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="G28" s="5">
-        <v>3.5999999999999997E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H28" s="5">
         <f t="shared" si="0"/>
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="I28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K28" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="L28" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="D29" t="s">
+        <v>142</v>
       </c>
       <c r="G29" s="5">
         <v>0.1</v>
       </c>
       <c r="H29" s="5">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J29" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K29" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="L29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>144</v>
+        <v>293</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>294</v>
       </c>
       <c r="G30" s="5">
-        <v>0.1</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="H30" s="5">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.252</v>
       </c>
       <c r="I30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K30" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="L30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="D31" t="s">
         <v>150</v>
@@ -2380,7 +2377,7 @@
       </c>
       <c r="H31" s="5">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="I31" t="s">
         <v>150</v>
@@ -2389,7 +2386,7 @@
         <v>151</v>
       </c>
       <c r="K31" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="L31" t="s">
         <v>152</v>
@@ -2397,23 +2394,23 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" t="s">
+        <v>279</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>280</v>
       </c>
       <c r="G32" s="5">
         <v>0.1</v>
       </c>
       <c r="H32" s="5">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
+        <f t="shared" ref="H32:H54" si="1">G32*A32</f>
+        <v>0.1</v>
       </c>
       <c r="I32" t="s">
         <v>154</v>
@@ -2422,7 +2419,7 @@
         <v>155</v>
       </c>
       <c r="K32" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="L32" t="s">
         <v>156</v>
@@ -2433,32 +2430,32 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>283</v>
+        <v>157</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D33" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="G33" s="5">
         <v>0.1</v>
       </c>
       <c r="H33" s="5">
-        <f t="shared" ref="H33:H55" si="1">G33*A33</f>
+        <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
       <c r="I33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K33" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -2466,13 +2463,13 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G34" s="5">
         <v>0.1</v>
@@ -2482,16 +2479,16 @@
         <v>0.1</v>
       </c>
       <c r="I34" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K34" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -2499,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G35" s="5">
         <v>0.1</v>
@@ -2515,70 +2512,70 @@
         <v>0.1</v>
       </c>
       <c r="I35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J35" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K35" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L35" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D36" t="s">
+        <v>281</v>
+      </c>
+      <c r="F36" t="s">
         <v>173</v>
       </c>
       <c r="G36" s="5">
-        <v>0.1</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="H36" s="5">
         <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="I36" t="s">
-        <v>173</v>
-      </c>
-      <c r="J36" t="s">
+        <v>0.44800000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
         <v>174</v>
       </c>
-      <c r="K36" t="s">
-        <v>106</v>
-      </c>
-      <c r="L36" t="s">
+      <c r="C37" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
-        <v>16</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="D37" t="s">
         <v>176</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F37" t="s">
-        <v>177</v>
-      </c>
       <c r="G37" s="5">
-        <v>2.8000000000000001E-2</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="H37" s="5">
         <f t="shared" si="1"/>
-        <v>0.44800000000000001</v>
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="I37" t="s">
+        <v>176</v>
+      </c>
+      <c r="J37" t="s">
+        <v>174</v>
+      </c>
+      <c r="K37" t="s">
+        <v>177</v>
+      </c>
+      <c r="L37" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -2586,70 +2583,61 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D38" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G38" s="5">
-        <v>4.0199999999999996</v>
+        <v>5.17</v>
       </c>
       <c r="H38" s="5">
         <f t="shared" si="1"/>
-        <v>4.0199999999999996</v>
+        <v>5.17</v>
       </c>
       <c r="I38" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J38" t="s">
+        <v>179</v>
+      </c>
+      <c r="K38" t="s">
+        <v>177</v>
+      </c>
+      <c r="L38" t="s">
         <v>178</v>
-      </c>
-      <c r="K38" t="s">
-        <v>181</v>
-      </c>
-      <c r="L38" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" t="s">
         <v>184</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>185</v>
       </c>
       <c r="G39" s="5">
-        <v>5.17</v>
+        <v>0.85</v>
       </c>
       <c r="H39" s="5">
         <f t="shared" si="1"/>
-        <v>5.17</v>
-      </c>
-      <c r="I39" t="s">
-        <v>185</v>
-      </c>
-      <c r="J39" t="s">
-        <v>183</v>
-      </c>
-      <c r="K39" t="s">
-        <v>181</v>
-      </c>
-      <c r="L39" t="s">
-        <v>182</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40" t="s">
         <v>186</v>
@@ -2660,48 +2648,60 @@
       <c r="D40" t="s">
         <v>188</v>
       </c>
-      <c r="E40" t="s">
-        <v>189</v>
-      </c>
       <c r="G40" s="5">
-        <v>0.85</v>
+        <v>3.6</v>
       </c>
       <c r="H40" s="5">
         <f t="shared" si="1"/>
-        <v>1.7</v>
+        <v>3.6</v>
+      </c>
+      <c r="I40" t="s">
+        <v>188</v>
+      </c>
+      <c r="J40" t="s">
+        <v>186</v>
+      </c>
+      <c r="K40" t="s">
+        <v>177</v>
+      </c>
+      <c r="L40" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B41" t="s">
         <v>190</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="D41" t="s">
-        <v>192</v>
+      <c r="E41" t="s">
+        <v>54</v>
       </c>
       <c r="G41" s="5">
-        <v>3.6</v>
+        <v>0.33</v>
       </c>
       <c r="H41" s="5">
         <f t="shared" si="1"/>
-        <v>3.6</v>
+        <v>0.66</v>
       </c>
       <c r="I41" t="s">
         <v>192</v>
       </c>
       <c r="J41" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K41" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="L41" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2709,122 +2709,119 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="E42" t="s">
-        <v>57</v>
+        <v>274</v>
+      </c>
+      <c r="D42" t="s">
+        <v>197</v>
       </c>
       <c r="G42" s="5">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="H42" s="5">
         <f t="shared" si="1"/>
-        <v>0.66</v>
+        <v>1.68</v>
       </c>
       <c r="I42" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J42" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K42" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="L42" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>278</v>
+        <v>202</v>
       </c>
       <c r="D43" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G43" s="5">
-        <v>0.84</v>
+        <v>0.47</v>
       </c>
       <c r="H43" s="5">
         <f t="shared" si="1"/>
-        <v>1.68</v>
-      </c>
-      <c r="I43" t="s">
-        <v>202</v>
-      </c>
-      <c r="J43" t="s">
-        <v>203</v>
-      </c>
-      <c r="K43" t="s">
-        <v>198</v>
-      </c>
-      <c r="L43" t="s">
-        <v>204</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
+        <v>204</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D44" t="s">
         <v>205</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D44" t="s">
-        <v>207</v>
-      </c>
       <c r="G44" s="5">
-        <v>0.47</v>
+        <v>1.03</v>
       </c>
       <c r="H44" s="5">
         <f t="shared" si="1"/>
-        <v>0.47</v>
+        <v>2.06</v>
+      </c>
+      <c r="I44" t="s">
+        <v>205</v>
+      </c>
+      <c r="J44" t="s">
+        <v>206</v>
+      </c>
+      <c r="K44" t="s">
+        <v>207</v>
+      </c>
+      <c r="L44" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="D45" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G45" s="5">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="H45" s="5">
         <f t="shared" si="1"/>
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="I45" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J45" t="s">
         <v>210</v>
       </c>
       <c r="K45" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="L45" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -2841,11 +2838,11 @@
         <v>216</v>
       </c>
       <c r="G46" s="5">
-        <v>1.87</v>
+        <v>2.46</v>
       </c>
       <c r="H46" s="5">
         <f t="shared" si="1"/>
-        <v>1.87</v>
+        <v>2.46</v>
       </c>
       <c r="I46" t="s">
         <v>216</v>
@@ -2854,7 +2851,7 @@
         <v>214</v>
       </c>
       <c r="K46" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="L46" t="s">
         <v>217</v>
@@ -2874,23 +2871,23 @@
         <v>220</v>
       </c>
       <c r="G47" s="5">
-        <v>2.46</v>
+        <v>1.69</v>
       </c>
       <c r="H47" s="5">
         <f t="shared" si="1"/>
-        <v>2.46</v>
+        <v>1.69</v>
       </c>
       <c r="I47" t="s">
         <v>220</v>
       </c>
       <c r="J47" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K47" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="L47" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -2898,32 +2895,32 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D48" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G48" s="5">
-        <v>1.69</v>
+        <v>0.46</v>
       </c>
       <c r="H48" s="5">
         <f t="shared" si="1"/>
-        <v>1.69</v>
+        <v>0.46</v>
       </c>
       <c r="I48" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J48" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K48" t="s">
-        <v>198</v>
+        <v>92</v>
       </c>
       <c r="L48" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -2931,32 +2928,32 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D49" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G49" s="5">
-        <v>0.46</v>
+        <v>1.42</v>
       </c>
       <c r="H49" s="5">
         <f t="shared" si="1"/>
-        <v>0.46</v>
+        <v>1.42</v>
       </c>
       <c r="I49" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J49" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K49" t="s">
-        <v>95</v>
+        <v>233</v>
       </c>
       <c r="L49" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -2964,32 +2961,20 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="D50" t="s">
-        <v>235</v>
+        <v>278</v>
       </c>
       <c r="G50" s="5">
-        <v>1.42</v>
+        <v>9.9600000000000009</v>
       </c>
       <c r="H50" s="5">
         <f t="shared" si="1"/>
-        <v>1.42</v>
-      </c>
-      <c r="I50" t="s">
-        <v>235</v>
-      </c>
-      <c r="J50" t="s">
-        <v>236</v>
-      </c>
-      <c r="K50" t="s">
-        <v>237</v>
-      </c>
-      <c r="L50" t="s">
-        <v>238</v>
+        <v>9.9600000000000009</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -2997,124 +2982,103 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D51" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G51" s="5">
-        <v>9.9600000000000009</v>
+        <v>4</v>
       </c>
       <c r="H51" s="5">
         <f t="shared" si="1"/>
-        <v>9.9600000000000009</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>1</v>
       </c>
-      <c r="B52" t="s">
-        <v>280</v>
+      <c r="B52" s="13" t="s">
+        <v>256</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D52" t="s">
-        <v>281</v>
+        <v>257</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>255</v>
       </c>
       <c r="G52" s="5">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="H52" s="5">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>259</v>
+        <v>284</v>
+      </c>
+      <c r="D53" s="12"/>
+      <c r="F53" t="s">
+        <v>285</v>
       </c>
       <c r="G53" s="5">
-        <v>0.7</v>
+        <v>5.24</v>
       </c>
       <c r="H53" s="5">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
-        <v>2</v>
+      <c r="A54" s="8">
+        <v>1</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>291</v>
+        <v>239</v>
       </c>
       <c r="D54" s="12"/>
       <c r="F54" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G54" s="5">
-        <v>5.24</v>
-      </c>
-      <c r="H54" s="5">
-        <f t="shared" si="1"/>
-        <v>10.48</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="8">
-        <v>1</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D55" s="12"/>
-      <c r="F55" t="s">
-        <v>292</v>
-      </c>
-      <c r="G55" s="5">
         <v>9.25</v>
       </c>
-      <c r="H55" s="9">
+      <c r="H54" s="9">
         <f t="shared" si="1"/>
         <v>9.25</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
-        <f>SUM(A2:A55)</f>
-        <v>195</v>
-      </c>
-      <c r="D56" t="s">
-        <v>57</v>
-      </c>
-      <c r="H56" s="10">
-        <f>SUM(H2:H55)</f>
-        <v>90.057000000000016</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B58" s="11" t="s">
-        <v>258</v>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <f>SUM(A2:A54)</f>
+        <v>193</v>
+      </c>
+      <c r="D55" t="s">
+        <v>54</v>
+      </c>
+      <c r="H55" s="10">
+        <f>SUM(H2:H54)</f>
+        <v>88.917000000000016</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B57" s="11" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3174,10 +3138,10 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" s="5">
         <v>0.13900000000000001</v>
@@ -3192,13 +3156,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
       </c>
       <c r="G3" s="5">
         <v>0.15</v>
@@ -3213,13 +3177,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D4" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
       </c>
       <c r="G4" s="5">
         <v>0.1</v>
@@ -3234,13 +3198,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G5" s="5">
         <v>0.17</v>
@@ -3255,13 +3219,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G6" s="5">
         <v>0.17</v>
@@ -3276,13 +3240,13 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G7" s="5">
         <v>5.3999999999999999E-2</v>
@@ -3297,13 +3261,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G8" s="5">
         <v>0.39</v>
@@ -3318,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G9" s="5">
         <v>1.41</v>
@@ -3339,13 +3303,13 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G10" s="5">
         <v>3.35</v>
@@ -3360,13 +3324,13 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G11" s="5">
         <v>0.14000000000000001</v>
@@ -3381,13 +3345,13 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G12" s="5">
         <v>1.1200000000000001</v>
@@ -3402,13 +3366,13 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G13" s="5">
         <v>0.02</v>
@@ -3423,13 +3387,13 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G14" s="5">
         <v>0.02</v>
@@ -3444,13 +3408,13 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G15" s="5">
         <v>0.14000000000000001</v>
@@ -3465,13 +3429,13 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G16" s="5">
         <v>0.35</v>
@@ -3486,13 +3450,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G17" s="5">
         <v>0.47</v>
@@ -3507,13 +3471,13 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G18" s="5">
         <v>0.59</v>
@@ -3528,13 +3492,13 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G19" s="5">
         <v>0.1</v>
@@ -3549,13 +3513,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G20" s="5">
         <v>0.1</v>
@@ -3570,13 +3534,13 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G21" s="5">
         <v>1.7000000000000001E-2</v>
@@ -3591,13 +3555,13 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G22" s="5">
         <v>0.1</v>
@@ -3612,13 +3576,13 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G23" s="5">
         <v>0.1</v>
@@ -3630,23 +3594,23 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>149</v>
+        <v>295</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>294</v>
       </c>
       <c r="G24" s="5">
-        <v>0.1</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="H24" s="5">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>8.4000000000000005E-2</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -3654,13 +3618,13 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="F25" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G25" s="5">
         <v>2.8000000000000001E-2</v>
@@ -3675,13 +3639,13 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D26" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G26" s="5">
         <v>4.0199999999999996</v>
@@ -3696,16 +3660,16 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D27" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E27" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G27" s="5">
         <v>0.85</v>
@@ -3720,13 +3684,13 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D28" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G28" s="5">
         <v>3.6</v>
@@ -3741,16 +3705,16 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E29" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G29" s="5">
         <v>0.33</v>
@@ -3765,13 +3729,13 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D30" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G30" s="5">
         <v>0.84</v>
@@ -3786,13 +3750,13 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G31" s="5">
         <v>2.46</v>
@@ -3807,13 +3771,13 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D32" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G32" s="5">
         <v>1.69</v>
@@ -3828,13 +3792,13 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D33" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G33" s="5">
         <v>9.9600000000000009</v>
@@ -3849,13 +3813,13 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D34" t="s">
         <v>277</v>
-      </c>
-      <c r="D34" t="s">
-        <v>281</v>
       </c>
       <c r="G34" s="5">
         <v>4</v>
@@ -3870,14 +3834,14 @@
         <v>1</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D35" s="12"/>
       <c r="F35" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G35" s="5">
         <v>5.24</v>
@@ -3892,14 +3856,14 @@
         <v>1</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D36" s="12"/>
       <c r="F36" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G36" s="5">
         <v>9.25</v>
@@ -3912,12 +3876,12 @@
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>SUM(A2:A36)</f>
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="10">
         <f>SUM(H2:H36)</f>
-        <v>58.559000000000005</v>
+        <v>58.443000000000005</v>
       </c>
     </row>
   </sheetData>
